--- a/artfynd/A 53674-2025 artfynd.xlsx
+++ b/artfynd/A 53674-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74412412</v>
+        <v>74966382</v>
       </c>
       <c r="B2" t="n">
-        <v>106294</v>
+        <v>110078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C2j 0038. SOM: Fraxinus excelsior. LEG: Göran Wendt, Vera Wendt, Signe Karlsson, Börje Wennberg</t>
+          <t>Smålands flora 2007: KOO: 5C2j 0038. SOM: Scorzonera humilis. LEG: Göran Wendt, Vera Wendt, Signe Karlsson, Börje Wennberg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Lövskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,7 +789,7 @@
         <v>74885607</v>
       </c>
       <c r="B3" t="n">
-        <v>104555</v>
+        <v>105049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,32 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74966382</v>
+        <v>74412412</v>
       </c>
       <c r="B4" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397955.3603782983</v>
+        <v>397955</v>
       </c>
       <c r="R4" t="n">
-        <v>6306665.289214393</v>
+        <v>6306665</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -970,24 +965,14 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-12-31</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 5C2j 0038. SOM: Scorzonera humilis. LEG: Göran Wendt, Vera Wendt, Signe Karlsson, Börje Wennberg</t>
+          <t>Smålands flora 2007: KOO: 5C2j 0038. SOM: Fraxinus excelsior. LEG: Göran Wendt, Vera Wendt, Signe Karlsson, Börje Wennberg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Lövskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
